--- a/docs/pins.xlsx
+++ b/docs/pins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\IchiPing\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3CC939-F8D2-41F6-81A9-D0E7B57BAEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80EDE18-659F-476D-96D5-BD3A9238FBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CB6A759-6E16-48D9-948C-B56A29EC017D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="85">
   <si>
     <t>MAX98357A</t>
     <phoneticPr fontId="2"/>
@@ -341,6 +341,38 @@
   </si>
   <si>
     <t>J2_12</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>speaker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mic</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>speaker +</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>speaker -</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RST</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D0</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -348,7 +380,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +407,15 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -407,7 +448,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -559,20 +600,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -620,7 +706,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -638,6 +724,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -653,6 +778,2816 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>235324</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>112058</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB3842F-6B67-B641-230C-E2F8D5B79C55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4807324" y="952500"/>
+          <a:ext cx="11205" cy="593912"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>134471</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>134470</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B250054-A2EB-42E3-89E1-796DAC26A33E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3272118" y="1535207"/>
+          <a:ext cx="1568823" cy="11205"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>156882</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3E0E1A7-C093-4C28-BE42-3F98DFA64F15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2655794" y="2263588"/>
+          <a:ext cx="638735" cy="11206"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11AF2EC5-D703-4337-A912-9320FF334184}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3249706" y="1546412"/>
+          <a:ext cx="11206" cy="739588"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8764629-2240-465E-9FD4-B7003B53B91B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2689412" y="4146176"/>
+          <a:ext cx="2812676" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="直線コネクタ 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8413661E-1764-4F98-B006-5F0B416FFC36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5502088" y="963706"/>
+          <a:ext cx="0" cy="3204882"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>14653</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="直線コネクタ 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D00809AE-EDB7-4C5D-A81E-1BF985531208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1773115" y="3311769"/>
+          <a:ext cx="667182" cy="925348"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>230841</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>107577</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59620ADD-8C1A-46A8-9584-640C26C0CDCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4134971" y="948017"/>
+          <a:ext cx="6724" cy="363071"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>146539</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>134470</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0616A86A-5A91-4E82-A1C6-BD84D0C5673A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2124808" y="1324450"/>
+          <a:ext cx="1966200" cy="23704"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>183173</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>212912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>227135</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A212D8-20EC-448A-8D6E-ADBB8F33381E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1941635" y="1436508"/>
+          <a:ext cx="2324358" cy="14223"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>112058</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D30906F0-AAB9-4B3F-AE58-34861DB4419B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4359087" y="974912"/>
+          <a:ext cx="11206" cy="459441"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>87923</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="直線コネクタ 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53948B0E-895B-41DF-B293-1CFEC1E5D676}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2066192" y="1335655"/>
+          <a:ext cx="24136" cy="2459691"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3879</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>115938</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>139211</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="直線コネクタ 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF1BE8C3-4C28-4019-837C-FF2DADDB0512}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1762341" y="3757419"/>
+          <a:ext cx="325832" cy="23273"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>212481</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>432</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>159469</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="直線コネクタ 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA94736-0CC1-4B87-AFB9-EAB0CF7471B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1948962" y="1436077"/>
+          <a:ext cx="29739" cy="2123084"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>212911</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="直線コネクタ 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71FC8F3A-8BB4-4988-AB63-43D5A2192FD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1781735" y="3451412"/>
+          <a:ext cx="235324" cy="11206"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>430</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>130592</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>18533</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>141798</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直線コネクタ 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92DEEF20-58D6-4E33-9FAC-866605AD5596}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1758892" y="3530284"/>
+          <a:ext cx="237910" cy="11206"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>186018</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>33618</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>51547</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="直線コネクタ 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D74C7A50-B7D9-4932-81F2-131C23B7C127}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3771900" y="1714500"/>
+          <a:ext cx="2537012" cy="6723"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>224118</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="直線コネクタ 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB387A0-CF21-4ED3-AF3A-A3D19675FAC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4000500" y="1423147"/>
+          <a:ext cx="0" cy="874059"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>212912</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="直線コネクタ 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F96C8596-B228-482C-9E3E-DECCB5040097}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3810000" y="2274794"/>
+          <a:ext cx="212912" cy="11206"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>6724</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>129988</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="直線コネクタ 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297097A8-74FE-4915-A510-3098536FECF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4713195" y="7978588"/>
+          <a:ext cx="2122393" cy="6724"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="71" name="直線コネクタ 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{794A80FC-0E68-416D-B489-4049D7291C22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6835588" y="7732059"/>
+          <a:ext cx="11206" cy="2151529"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>201706</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>168088</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="直線コネクタ 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76166A36-A69B-4457-ADC7-D2719581C256}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3563471" y="9177617"/>
+          <a:ext cx="3272117" cy="22412"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>197224</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>134471</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="直線コネクタ 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0EABFF8-3B3C-4221-819E-A6870643EACC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4679577" y="8919882"/>
+          <a:ext cx="2178423" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>197224</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>107576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="直線コネクタ 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EC5408-02C2-46C7-BD79-38D5EFF2A5EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4679577" y="9845488"/>
+          <a:ext cx="2167217" cy="26894"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>13448</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="83" name="直線コネクタ 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F03DDF6-5FEC-456F-9B5E-619B25330CC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2030507" y="7967382"/>
+          <a:ext cx="1331258" cy="2242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>143436</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>109818</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="85" name="直線コネクタ 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C27B2019-0290-402D-8D43-5CED7AA7F951}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2160495" y="7709647"/>
+          <a:ext cx="2333064" cy="20171"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>116541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>172571</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="87" name="直線コネクタ 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBB88525-36BF-4515-ACB6-2A4AD65D359A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2633382" y="7736541"/>
+          <a:ext cx="4483" cy="2102224"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>156882</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>58271</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="89" name="直線コネクタ 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF82A1A2-A4B8-432A-83BB-8703782A824A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2622176" y="9796183"/>
+          <a:ext cx="1905000" cy="266699"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>117230</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>85595</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>229979</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="91" name="直線コネクタ 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36814F29-68AF-48E2-8450-3D133089BC04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2659673" y="2066192"/>
+          <a:ext cx="2701307" cy="3270652"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>197827</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>131885</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="94" name="直線コネクタ 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC864AE8-5BB8-45B5-83E8-AA7EB2A13E20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2615712" y="2542442"/>
+          <a:ext cx="3011365" cy="2820866"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>7327</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>234462</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="97" name="直線コネクタ 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8F283FB-36D9-4843-9029-96BC9148A2A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2645019" y="2769577"/>
+          <a:ext cx="2520462" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>212480</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>124558</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>131885</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="100" name="直線コネクタ 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CB99615-B048-447F-A396-BD65F0ADBAAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2630365" y="996462"/>
+          <a:ext cx="131885" cy="2051538"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>227135</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>117231</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>153866</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="104" name="直線コネクタ 103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A172ADCA-3C5C-421F-A970-F38908A56B22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2659673" y="959827"/>
+          <a:ext cx="315058" cy="2593731"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>227135</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>139211</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="107" name="直線コネクタ 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F71EE0E-6A6E-4634-BC6A-FCB5960888D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2667000" y="959827"/>
+          <a:ext cx="549519" cy="2828192"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>139211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>124558</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>43962</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="110" name="直線コネクタ 109">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CDCC628-D3B9-4CE0-895B-DEB8818AF0E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1729154" y="2088173"/>
+          <a:ext cx="1912327" cy="3062654"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>197827</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>102577</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>36635</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="113" name="直線コネクタ 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2374A38D-B440-4D7D-8BF0-B8496B5B8B2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1736481" y="2315308"/>
+          <a:ext cx="783981" cy="2828192"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>102577</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="115" name="直線コネクタ 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD769C5-CC1A-4131-8D3C-716BEE3B64A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1729154" y="2557096"/>
+          <a:ext cx="1230923" cy="2579077"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>212480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>124558</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>51288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="118" name="直線コネクタ 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785F02FF-75B4-41E8-82F2-5194E749C691}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3172558" y="2161442"/>
+          <a:ext cx="3106615" cy="3238500"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>80597</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>234461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="121" name="直線コネクタ 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B346B5C-6772-471B-B2A9-1A1BA8191650}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3377712" y="2183423"/>
+          <a:ext cx="2227384" cy="3245827"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>234461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>124558</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="124" name="直線コネクタ 123">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED655252-5004-4FA4-B7F1-271AC06651C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3612173" y="2183423"/>
+          <a:ext cx="1348154" cy="3253154"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>131885</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="127" name="直線コネクタ 126">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47C8430B-4176-4E4E-9CEB-C945C8D9F3DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3846635" y="2205404"/>
+          <a:ext cx="461596" cy="3223846"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>146539</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>197826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>139212</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="131" name="直線コネクタ 130">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8131CAE-E0E8-49DA-8665-667066EF5D32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3663462" y="2146788"/>
+          <a:ext cx="432288" cy="3289789"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>227135</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>139211</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36634</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="134" name="直線コネクタ 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B36A521-6529-48CB-9C61-92A76EB3779C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3626827" y="2659673"/>
+          <a:ext cx="908538" cy="2725615"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>161192</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>241788</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>117230</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="137" name="直線コネクタ 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA4CC78D-AEAA-44D6-AAF8-B835F7136860}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4557346" y="5590442"/>
+          <a:ext cx="175846" cy="4982308"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>102577</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>14654</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="140" name="直線コネクタ 139">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFDB294E-7DAE-4A22-9DAF-F25AA4526AB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2520462" y="5297365"/>
+          <a:ext cx="1890346" cy="3377712"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>80597</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>168520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="143" name="直線コネクタ 142">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F951F08C-9D1D-48A4-A771-5FCF9158E5DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4037135" y="5275385"/>
+          <a:ext cx="381000" cy="3121269"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>117231</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>87923</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="155" name="直線コネクタ 154">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68D40B1A-C69A-4F98-B46D-3307DDA5CD1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3634154" y="5290038"/>
+          <a:ext cx="849923" cy="3575539"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>14654</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>227134</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>117231</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>131885</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="161" name="直線コネクタ 160">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C845E8D-FD75-4323-841E-1DD927108181}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3531577" y="5575788"/>
+          <a:ext cx="2960077" cy="3319097"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>175847</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="165" name="直線コネクタ 164">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64D5310E-D9DB-47FB-BFF9-0C2F5C33B559}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3472962" y="5597769"/>
+          <a:ext cx="2791557" cy="3531577"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>183173</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>218343</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>115765</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="177" name="直線コネクタ 176">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820345E6-CB72-4009-A200-61B99A25EE10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1062404" y="3751385"/>
+          <a:ext cx="474785" cy="5861"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>197827</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2414</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>111025</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="178" name="直線コネクタ 177">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50B60CC7-996E-497C-A023-398B879C8821}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1077058" y="3509596"/>
+          <a:ext cx="464010" cy="1121"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -952,18 +3887,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB69EE91-C5E4-4044-B9FD-8892132CAEF2}">
-  <dimension ref="E3:BM27"/>
+  <dimension ref="E3:BE51"/>
   <sheetFormatPr defaultColWidth="2.875" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="44" max="44" width="11.125" customWidth="1"/>
-    <col min="56" max="56" width="3" customWidth="1"/>
-    <col min="57" max="57" width="11.5" customWidth="1"/>
-    <col min="58" max="58" width="8.125" customWidth="1"/>
-    <col min="64" max="64" width="10.125" customWidth="1"/>
-    <col min="65" max="65" width="20.125" customWidth="1"/>
+    <col min="48" max="48" width="3" customWidth="1"/>
+    <col min="49" max="49" width="11.5" customWidth="1"/>
+    <col min="50" max="50" width="8.125" customWidth="1"/>
+    <col min="56" max="56" width="10.125" customWidth="1"/>
+    <col min="57" max="57" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="5:65" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="5:57" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F3">
         <v>1</v>
       </c>
@@ -1042,95 +3977,98 @@
       <c r="AE3">
         <v>6</v>
       </c>
+      <c r="AO3" t="s">
+        <v>77</v>
+      </c>
     </row>
-    <row r="4" spans="5:65" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="5:57" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="22" t="s">
+      <c r="F4" s="25"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="O4" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="19" t="s">
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="20" t="s">
+      <c r="T4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="U4" s="21" t="s">
+      <c r="U4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="19" t="s">
+      <c r="V4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="19" t="s">
+      <c r="W4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="19" t="s">
+      <c r="X4" s="15"/>
+      <c r="Y4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="7"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="26"/>
       <c r="AO4" t="s">
         <v>0</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="AV4" t="s">
         <v>3</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BC4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="5" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="27"/>
       <c r="AO5">
         <v>1</v>
       </c>
@@ -1140,55 +4078,55 @@
       <c r="AR5" t="s">
         <v>67</v>
       </c>
-      <c r="BD5">
+      <c r="AV5">
         <v>1</v>
       </c>
+      <c r="AW5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC5">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>37</v>
+      </c>
       <c r="BE5" t="s">
-        <v>18</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK5">
-        <v>1</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>37</v>
-      </c>
-      <c r="BM5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="6" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="27"/>
       <c r="AO6">
         <v>2</v>
       </c>
@@ -1198,55 +4136,55 @@
       <c r="AR6" t="s">
         <v>69</v>
       </c>
-      <c r="BD6">
+      <c r="AV6">
         <v>2</v>
       </c>
+      <c r="AW6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC6">
+        <v>2</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>19</v>
+      </c>
       <c r="BE6" t="s">
-        <v>12</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>49</v>
-      </c>
-      <c r="BK6">
-        <v>2</v>
-      </c>
-      <c r="BL6" t="s">
         <v>19</v>
       </c>
-      <c r="BM6" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="7" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="7" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E7">
         <v>4</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="27"/>
       <c r="AO7">
         <v>3</v>
       </c>
@@ -1256,46 +4194,56 @@
       <c r="AR7" t="s">
         <v>70</v>
       </c>
-      <c r="BD7">
+      <c r="AV7">
         <v>3</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="AW7" t="s">
         <v>13</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="AX7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="8" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="27"/>
       <c r="AO8">
         <v>4</v>
       </c>
@@ -1305,49 +4253,63 @@
       <c r="AR8" t="s">
         <v>19</v>
       </c>
-      <c r="BD8">
+      <c r="AV8">
         <v>4</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="AW8" t="s">
         <v>14</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="AX8" t="s">
         <v>63</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="BC8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="9" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E9">
         <v>6</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="27"/>
       <c r="AO9">
         <v>5</v>
       </c>
@@ -1357,55 +4319,61 @@
       <c r="AR9" t="s">
         <v>50</v>
       </c>
-      <c r="BD9">
+      <c r="AV9">
         <v>5</v>
       </c>
+      <c r="AW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC9">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>38</v>
+      </c>
       <c r="BE9" t="s">
-        <v>15</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>64</v>
-      </c>
-      <c r="BK9">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>38</v>
-      </c>
-      <c r="BM9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="10" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E10">
         <v>7</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="27"/>
       <c r="AO10">
         <v>6</v>
       </c>
@@ -1415,55 +4383,61 @@
       <c r="AR10" t="s">
         <v>19</v>
       </c>
-      <c r="BD10">
+      <c r="AV10">
         <v>6</v>
       </c>
+      <c r="AW10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>66</v>
+      </c>
+      <c r="BC10">
+        <v>2</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>19</v>
+      </c>
       <c r="BE10" t="s">
-        <v>16</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>66</v>
-      </c>
-      <c r="BK10">
-        <v>2</v>
-      </c>
-      <c r="BL10" t="s">
         <v>19</v>
       </c>
-      <c r="BM10" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="11" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="11" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E11">
         <v>8</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="27"/>
       <c r="AO11">
         <v>7</v>
       </c>
@@ -1473,711 +4447,976 @@
       <c r="AR11" t="s">
         <v>49</v>
       </c>
-      <c r="BD11">
+      <c r="AV11">
         <v>7</v>
       </c>
-      <c r="BE11" t="s">
+      <c r="AW11" t="s">
         <v>17</v>
       </c>
-      <c r="BF11" t="s">
+      <c r="AX11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="12" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E12">
         <v>9</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="8"/>
-      <c r="BD12">
+      <c r="F12" s="9"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="27"/>
+      <c r="AP12" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV12">
         <v>8</v>
       </c>
-      <c r="BE12" t="s">
+      <c r="AW12" t="s">
         <v>19</v>
       </c>
-      <c r="BF12" t="s">
+      <c r="AX12" t="s">
         <v>19</v>
       </c>
-      <c r="BK12" t="s">
+      <c r="BC12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="13" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="8"/>
-      <c r="AO13" t="s">
+      <c r="F13" s="9"/>
+      <c r="G13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="27"/>
+      <c r="AP13" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AV13">
+        <v>9</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>50</v>
+      </c>
+      <c r="BC13">
         <v>1</v>
       </c>
-      <c r="BD13">
-        <v>9</v>
+      <c r="BD13" t="s">
+        <v>41</v>
       </c>
       <c r="BE13" t="s">
-        <v>20</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>50</v>
-      </c>
-      <c r="BK13">
-        <v>1</v>
-      </c>
-      <c r="BL13" t="s">
-        <v>41</v>
-      </c>
-      <c r="BM13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="14" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="8"/>
-      <c r="AO14">
-        <v>1</v>
-      </c>
-      <c r="AP14" t="s">
+      <c r="F14" s="9"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="27"/>
+      <c r="BC14">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="s">
         <v>19</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="BE14" t="s">
         <v>19</v>
       </c>
-      <c r="BK14">
-        <v>2</v>
-      </c>
-      <c r="BL14" t="s">
-        <v>19</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="15" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="15" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E15">
         <v>2</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="8"/>
-      <c r="AO15">
-        <v>2</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>30</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>50</v>
-      </c>
-      <c r="BD15" t="s">
+      <c r="F15" s="9"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="27"/>
+      <c r="AV15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="16" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E16">
         <v>3</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2"/>
-      <c r="AE16" s="8"/>
-      <c r="AO16">
-        <v>3</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>27</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD16">
+      <c r="F16" s="9"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="27"/>
+      <c r="AO16" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV16" s="23">
         <v>1</v>
       </c>
-      <c r="BE16" t="s">
+      <c r="AW16" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="BF16" t="s">
+      <c r="AX16" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="BK16" t="s">
+      <c r="BC16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="17" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E17">
         <v>4</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-      <c r="AE17" s="8"/>
-      <c r="AO17">
-        <v>4</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>13</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD17">
+      <c r="F17" s="9"/>
+      <c r="G17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="27"/>
+      <c r="AO17" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="23">
         <v>2</v>
       </c>
+      <c r="AW17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="BC17">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>40</v>
+      </c>
       <c r="BE17" t="s">
-        <v>19</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="BK17">
-        <v>1</v>
-      </c>
-      <c r="BL17" t="s">
-        <v>40</v>
-      </c>
-      <c r="BM17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="18" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E18">
         <v>5</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-      <c r="AD18" s="2"/>
-      <c r="AE18" s="8"/>
-      <c r="AO18">
-        <v>5</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>31</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>67</v>
-      </c>
-      <c r="BD18">
+      <c r="F18" s="9"/>
+      <c r="G18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="27"/>
+      <c r="AO18" s="23">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ18" s="23"/>
+      <c r="AR18" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AV18" s="23">
         <v>3</v>
       </c>
+      <c r="AW18" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX18" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="BC18">
+        <v>2</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>19</v>
+      </c>
       <c r="BE18" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF18" t="s">
-        <v>48</v>
-      </c>
-      <c r="BK18">
-        <v>2</v>
-      </c>
-      <c r="BL18" t="s">
         <v>19</v>
       </c>
-      <c r="BM18" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="19" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="19" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E19">
         <v>6</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="8"/>
-      <c r="AO19">
-        <v>6</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>32</v>
-      </c>
-      <c r="AR19" t="s">
+      <c r="F19" s="9"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="27"/>
+      <c r="AO19" s="23">
+        <v>2</v>
+      </c>
+      <c r="AP19" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="5:65" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="5:57" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="E20">
         <v>7</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="8"/>
-      <c r="BD20" t="s">
+      <c r="F20" s="9"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="27"/>
+      <c r="AO20" s="23">
+        <v>3</v>
+      </c>
+      <c r="AP20" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ20" s="23"/>
+      <c r="AR20" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV20" t="s">
         <v>11</v>
       </c>
-      <c r="BK20" t="s">
+      <c r="BC20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="5:65" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="5:57" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6"/>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="6"/>
-      <c r="AO21" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD21">
+      <c r="F21" s="9"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AO21" s="23">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ21" s="23"/>
+      <c r="AR21" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV21">
         <v>1</v>
       </c>
+      <c r="AW21" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC21">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>39</v>
+      </c>
       <c r="BE21" t="s">
-        <v>20</v>
-      </c>
-      <c r="BF21" t="s">
-        <v>49</v>
-      </c>
-      <c r="BK21">
-        <v>1</v>
-      </c>
-      <c r="BL21" t="s">
-        <v>39</v>
-      </c>
-      <c r="BM21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="5:65" x14ac:dyDescent="0.4">
+    <row r="22" spans="5:57" x14ac:dyDescent="0.4">
       <c r="E22">
         <v>9</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="12" t="s">
+      <c r="F22" s="9"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="12" t="s">
+      <c r="M22" s="8"/>
+      <c r="N22" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="12" t="s">
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="23" t="s">
+      <c r="R22" s="8"/>
+      <c r="S22" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="T22" s="10"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="2"/>
-      <c r="AO22">
-        <v>1</v>
-      </c>
-      <c r="AP22" t="s">
+      <c r="T22" s="9"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="17"/>
+      <c r="AO22" s="23">
+        <v>5</v>
+      </c>
+      <c r="AP22" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ22" s="23"/>
+      <c r="AR22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV22">
+        <v>2</v>
+      </c>
+      <c r="AW22" t="s">
         <v>19</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AX22" t="s">
         <v>19</v>
       </c>
-      <c r="BD22">
+      <c r="BC22">
         <v>2</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>19</v>
       </c>
       <c r="BE22" t="s">
         <v>19</v>
       </c>
-      <c r="BF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="BK22">
-        <v>2</v>
-      </c>
-      <c r="BL22" t="s">
-        <v>19</v>
-      </c>
-      <c r="BM22" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="23" spans="5:65" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="5:57" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="13" t="s">
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="P23" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="Q23" s="13" t="s">
+      <c r="Q23" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="R23" s="13" t="s">
+      <c r="R23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="14" t="s">
+      <c r="S23" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="T23" s="10"/>
-      <c r="U23" s="12" t="s">
+      <c r="T23" s="9"/>
+      <c r="U23" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="V23" s="12" t="s">
+      <c r="V23" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="W23" s="9"/>
-      <c r="X23" s="12" t="s">
+      <c r="W23" s="8"/>
+      <c r="X23" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="Y23" s="12" t="s">
+      <c r="Y23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="Z23" s="12" t="s">
+      <c r="Z23" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AA23" s="15" t="s">
+      <c r="AA23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="12" t="s">
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="AD23" s="12" t="s">
+      <c r="AD23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="AE23" s="2"/>
-      <c r="AO23">
+      <c r="AE23" s="17"/>
+      <c r="AO23" s="23">
+        <v>6</v>
+      </c>
+      <c r="AP23" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ23" s="23"/>
+      <c r="AR23" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV23">
+        <v>3</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="5:57" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="AV24">
+        <v>4</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="AO25" t="s">
         <v>2</v>
       </c>
-      <c r="AP23" t="s">
+      <c r="BC25">
+        <v>1</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BE25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="5:57" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="AO26" s="23">
+        <v>1</v>
+      </c>
+      <c r="AP26" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ26" s="23"/>
+      <c r="AR26" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="BC26">
+        <v>2</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>19</v>
+      </c>
+      <c r="BE26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="5:57" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="N27" s="4"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="6"/>
+      <c r="AO27" s="23">
+        <v>2</v>
+      </c>
+      <c r="AP27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="AR23" t="s">
+      <c r="AQ27" s="23"/>
+      <c r="AR27" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="BD23">
+    </row>
+    <row r="28" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="N28" s="1"/>
+      <c r="W28" s="7"/>
+      <c r="AO28" s="23">
         <v>3</v>
       </c>
-      <c r="BE23" t="s">
-        <v>22</v>
+      <c r="AP28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ28" s="23"/>
+      <c r="AR28" s="23" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="24" spans="5:65" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="AO24">
-        <v>3</v>
-      </c>
-      <c r="AP24" t="s">
+    <row r="29" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="N29" s="1"/>
+      <c r="W29" s="7"/>
+      <c r="AO29" s="23">
+        <v>4</v>
+      </c>
+      <c r="AP29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ29" s="23"/>
+      <c r="AR29" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="N30" s="1"/>
+      <c r="W30" s="7"/>
+      <c r="AO30" s="23">
+        <v>5</v>
+      </c>
+      <c r="AP30" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ30" s="23"/>
+      <c r="AR30" s="23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="N31" s="1"/>
+      <c r="W31" s="7"/>
+      <c r="AO31" s="23">
+        <v>1</v>
+      </c>
+      <c r="AP31" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ31" s="23"/>
+      <c r="AR31" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW31" s="24"/>
+    </row>
+    <row r="32" spans="5:57" x14ac:dyDescent="0.4">
+      <c r="N32" s="1"/>
+      <c r="W32" s="7"/>
+    </row>
+    <row r="33" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="P33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="W33" s="7"/>
+      <c r="AE33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="I34" t="s">
+        <v>49</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="P34" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="W34" s="7"/>
+    </row>
+    <row r="35" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N35" s="1"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="W35" s="7"/>
+    </row>
+    <row r="36" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N36" s="1"/>
+      <c r="P36" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="W36" s="7"/>
+    </row>
+    <row r="37" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N37" s="1"/>
+      <c r="P37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W37" s="7"/>
+    </row>
+    <row r="38" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N38" s="1"/>
+      <c r="P38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AR24" t="s">
-        <v>57</v>
-      </c>
-      <c r="BD24">
-        <v>4</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>23</v>
-      </c>
-      <c r="BK24" t="s">
-        <v>9</v>
-      </c>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="W38" s="7"/>
     </row>
-    <row r="25" spans="5:65" x14ac:dyDescent="0.4">
-      <c r="AO25">
-        <v>4</v>
-      </c>
-      <c r="AP25" t="s">
+    <row r="39" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N39" s="1"/>
+      <c r="P39" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="AR25" t="s">
-        <v>50</v>
-      </c>
-      <c r="BK25">
-        <v>1</v>
-      </c>
-      <c r="BL25" t="s">
-        <v>36</v>
-      </c>
-      <c r="BM25" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="W39" s="7"/>
     </row>
-    <row r="26" spans="5:65" x14ac:dyDescent="0.4">
-      <c r="AO26">
-        <v>5</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>49</v>
-      </c>
-      <c r="BK26">
-        <v>2</v>
-      </c>
-      <c r="BL26" t="s">
+    <row r="40" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N40" s="1"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="W40" s="7"/>
+    </row>
+    <row r="41" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N41" s="1"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="W41" s="7"/>
+    </row>
+    <row r="42" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N42" s="1"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="W42" s="7"/>
+    </row>
+    <row r="43" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N43" s="1"/>
+      <c r="P43" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="BM26" t="s">
-        <v>19</v>
-      </c>
+      <c r="W43" s="7"/>
     </row>
-    <row r="27" spans="5:65" x14ac:dyDescent="0.4">
-      <c r="AO27">
-        <v>6</v>
-      </c>
-      <c r="AP27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>19</v>
-      </c>
+    <row r="44" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N44" s="1"/>
+      <c r="P44" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="W44" s="7"/>
     </row>
+    <row r="45" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N45" s="1"/>
+      <c r="W45" s="7"/>
+    </row>
+    <row r="46" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N46" s="1"/>
+      <c r="W46" s="7"/>
+    </row>
+    <row r="47" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N47" s="1"/>
+      <c r="W47" s="7"/>
+    </row>
+    <row r="48" spans="9:31" x14ac:dyDescent="0.4">
+      <c r="N48" s="1"/>
+      <c r="W48" s="7"/>
+    </row>
+    <row r="49" spans="14:23" x14ac:dyDescent="0.4">
+      <c r="N49" s="1"/>
+      <c r="W49" s="7"/>
+    </row>
+    <row r="50" spans="14:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="N50" s="2"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="34"/>
+    </row>
+    <row r="51" spans="14:23" ht="19.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>